--- a/data/osmar.xlsx
+++ b/data/osmar.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lsuagctr-my.sharepoint.com/personal/rtomaz_agcenter_lsu_edu/Documents/Documents/GitHub/paper_TS_weather/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E42CC2-15FE-4039-868A-F1D2524D972A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{47E42CC2-15FE-4039-868A-F1D2524D972A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50DA6CE3-12ED-4078-8106-C71A73D629BD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{17BCDCEB-25BA-4A6C-A962-5CACED761CDA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{17BCDCEB-25BA-4A6C-A962-5CACED761CDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$A$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="23">
   <si>
     <t>Tratamento</t>
   </si>
@@ -91,6 +94,9 @@
   </si>
   <si>
     <t>2AE_10^6</t>
+  </si>
+  <si>
+    <t>trat</t>
   </si>
 </sst>
 </file>
@@ -127,7 +133,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -150,22 +156,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -186,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,7 +246,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -332,7 +352,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -474,7 +494,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -482,14 +502,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE550A1-A59F-4A7E-B563-86FB73872A55}">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,8 +522,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -517,7 +540,7 @@
         <v>44791.666666666672</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -530,8 +553,11 @@
       <c r="D3" s="4">
         <v>55468.75</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -544,8 +570,11 @@
       <c r="D4" s="4">
         <v>106480.55555555556</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -558,8 +587,11 @@
       <c r="D5" s="4">
         <v>49324.324324324327</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -572,8 +604,11 @@
       <c r="D6" s="4">
         <v>83714.285714285725</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -586,8 +621,11 @@
       <c r="D7" s="4">
         <v>97058.823529411762</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -600,8 +638,11 @@
       <c r="D8" s="4">
         <v>23863.636363636364</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -614,8 +655,11 @@
       <c r="D9" s="4">
         <v>26250</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -628,8 +672,11 @@
       <c r="D10" s="4">
         <v>67753.57142857142</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -642,8 +689,11 @@
       <c r="D11" s="4">
         <v>66739.130434782608</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -656,8 +706,11 @@
       <c r="D12" s="4">
         <v>89285.71428571429</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -670,8 +723,11 @@
       <c r="D13" s="4">
         <v>68750</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -684,8 +740,11 @@
       <c r="D14" s="4">
         <v>60576.923076923078</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -698,8 +757,11 @@
       <c r="D15" s="4">
         <v>56481.481481481474</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -712,8 +774,11 @@
       <c r="D16" s="4">
         <v>62878.787878787873</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -726,8 +791,11 @@
       <c r="D17" s="4">
         <v>72413.793103448275</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -740,8 +808,11 @@
       <c r="D18" s="4">
         <v>36263.73626373626</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -754,8 +825,11 @@
       <c r="D19" s="4">
         <v>71951.219512195123</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -769,7 +843,7 @@
         <v>32142.857142857145</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -783,7 +857,7 @@
         <v>58962.264150943396</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -797,7 +871,7 @@
         <v>62765.957446808512</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -811,7 +885,7 @@
         <v>55882.352941176468</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -825,7 +899,7 @@
         <v>88414.634146341472</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -839,7 +913,7 @@
         <v>42441.860465116282</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -853,7 +927,7 @@
         <v>66666.666666666672</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>8</v>
       </c>
@@ -867,7 +941,7 @@
         <v>79861.111111111109</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>8</v>
       </c>
@@ -881,7 +955,7 @@
         <v>43229.166666666672</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -895,7 +969,7 @@
         <v>49999.999999999993</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>8</v>
       </c>
@@ -909,7 +983,7 @@
         <v>97881.355932203398</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>8</v>
       </c>
@@ -923,7 +997,7 @@
         <v>63970.588235294112</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -2016,6 +2090,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A109" xr:uid="{5AE550A1-A59F-4A7E-B563-86FB73872A55}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>